--- a/Excel/SkillDivineAttrConfig.xlsx
+++ b/Excel/SkillDivineAttrConfig.xlsx
@@ -56,22 +56,22 @@
     <t>string</t>
   </si>
   <si>
-    <t>神技·刺杀剑法</t>
-  </si>
-  <si>
-    <t>刺杀剑术敌人距离每多一格，所受伤害提高{0}%</t>
-  </si>
-  <si>
-    <t>神技·雷电术</t>
-  </si>
-  <si>
-    <t>雷电术可以重复攻击同一目标，最多{0}下</t>
-  </si>
-  <si>
-    <t>神技·火符术</t>
-  </si>
-  <si>
-    <t>火符术可以弹射3格内的其他敌人，最多弹射{0}次，不会重复弹射</t>
+    <t>神技·穿刺剑法</t>
+  </si>
+  <si>
+    <t>穿刺剑法敌人距离每多一格，所受伤害提高{0}%</t>
+  </si>
+  <si>
+    <t>神技·神雷术</t>
+  </si>
+  <si>
+    <t>神雷术可以重复攻击同一目标，最多{0}下</t>
+  </si>
+  <si>
+    <t>神技·火符道法</t>
+  </si>
+  <si>
+    <t>火符道法可以弹射3格内的其他敌人，最多弹射{0}次，不会重复弹射</t>
   </si>
   <si>
     <t>神技·武力盾</t>
@@ -80,10 +80,10 @@
     <t>武力盾额外提高{0}的绝对减伤</t>
   </si>
   <si>
-    <t>神技·魔法盾</t>
-  </si>
-  <si>
-    <t>魔法盾额外提高{0}的二次闪避</t>
+    <t>神技·法力盾</t>
+  </si>
+  <si>
+    <t>法力盾额外提高{0}的二次闪避</t>
   </si>
   <si>
     <t>神技·道力盾</t>

--- a/Excel/SkillDivineAttrConfig.xlsx
+++ b/Excel/SkillDivineAttrConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>_Id</t>
   </si>
@@ -90,6 +90,24 @@
   </si>
   <si>
     <t>月灵获得{0}%系数的道力盾（无需人物上阵技能）</t>
+  </si>
+  <si>
+    <t>神技·战吼</t>
+  </si>
+  <si>
+    <t>每次使用提高{0}%生命倍率，神话之路削弱150倍，最多叠加6次</t>
+  </si>
+  <si>
+    <t>神技·心灵传送</t>
+  </si>
+  <si>
+    <t>每次使用提高{0}%魔法倍率，神话之路削弱150倍，最多叠加6次</t>
+  </si>
+  <si>
+    <t>神技·隐身道法</t>
+  </si>
+  <si>
+    <t>每次使用提高自己和宠物{0}%道术倍率和{0}%生命倍率，神话之路削弱150倍，最多叠加6次</t>
   </si>
 </sst>
 </file>
@@ -1048,12 +1066,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:L11"/>
+  <dimension ref="C1:L14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="13.375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="45.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="53" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.25" style="1" customWidth="1"/>
     <col min="8" max="8" width="10.125" style="1" customWidth="1"/>
     <col min="9" max="9" width="10.5" style="1" customWidth="1"/>
@@ -1263,6 +1281,66 @@
       </c>
       <c r="L11" s="1"/>
     </row>
+    <row r="12" spans="3:8">
+      <c r="C12" s="2">
+        <v>4</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1008</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="3:8">
+      <c r="C13" s="2">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1">
+        <v>2008</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="3:8">
+      <c r="C14" s="2">
+        <v>6</v>
+      </c>
+      <c r="D14" s="1">
+        <v>3008</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:G3 E4:G4 E5:F5 C3:C5 D4:D5 L3:L5" errorStyle="warning">

--- a/Excel/SkillDivineAttrConfig.xlsx
+++ b/Excel/SkillDivineAttrConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="36">
   <si>
     <t>_Id</t>
   </si>
@@ -47,6 +47,12 @@
     <t>Param</t>
   </si>
   <si>
+    <t>ParamRate</t>
+  </si>
+  <si>
+    <t>PercentRate</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -92,6 +98,9 @@
     <t>月灵获得{0}%系数的道力盾（无需人物上阵技能）</t>
   </si>
   <si>
+    <t>#</t>
+  </si>
+  <si>
     <t>神技·战吼</t>
   </si>
   <si>
@@ -108,6 +117,24 @@
   </si>
   <si>
     <t>每次使用提高自己和宠物{0}%道术倍率和{0}%生命倍率，神话之路削弱150倍，最多叠加6次</t>
+  </si>
+  <si>
+    <t>神技·裂地斩</t>
+  </si>
+  <si>
+    <t>裂地斩增加{0}%的触发概率，神话之路会削弱</t>
+  </si>
+  <si>
+    <t>神技·分身术</t>
+  </si>
+  <si>
+    <t>分身享受{0}%的天赋和无视防御效果，神话之路会削弱</t>
+  </si>
+  <si>
+    <t>神技·无极道体</t>
+  </si>
+  <si>
+    <t>宠物享受{0}%的天赋和无视防御效果，神话之路会削弱</t>
   </si>
 </sst>
 </file>
@@ -1066,24 +1093,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:L14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
+  <dimension ref="A3:L20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="13.375" style="1" customWidth="1"/>
     <col min="6" max="6" width="53" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5" style="1" customWidth="1"/>
+    <col min="8" max="9" width="10.125" style="1" customWidth="1"/>
     <col min="10" max="10" width="14.875" style="1" customWidth="1"/>
     <col min="11" max="11" width="14.375" style="1" customWidth="1"/>
     <col min="12" max="12" width="17.25" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16" customHeight="1"/>
-    <row r="2" ht="16" customHeight="1"/>
-    <row r="3" s="1" customFormat="1" ht="16" customHeight="1" spans="3:12">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1102,14 +1126,18 @@
       <c r="H3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
+      <c r="I3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="16" customHeight="1" spans="3:12">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C4" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>1</v>
@@ -1126,36 +1154,44 @@
       <c r="H4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="I4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" ht="16" customHeight="1" spans="3:12">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C5" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="16" customHeight="1" spans="3:12">
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C6" s="2">
         <v>10021</v>
       </c>
@@ -1163,10 +1199,10 @@
         <v>1002</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G6" s="2">
         <v>2</v>
@@ -1174,9 +1210,15 @@
       <c r="H6" s="2">
         <v>30</v>
       </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1</v>
+      </c>
       <c r="L6" s="1"/>
     </row>
-    <row r="7" s="2" customFormat="1" ht="16" customHeight="1" spans="3:12">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C7" s="2">
         <v>20021</v>
       </c>
@@ -1184,10 +1226,10 @@
         <v>2002</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -1195,9 +1237,15 @@
       <c r="H7" s="2">
         <v>1</v>
       </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1</v>
+      </c>
       <c r="L7" s="1"/>
     </row>
-    <row r="8" s="2" customFormat="1" ht="16" customHeight="1" spans="3:12">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C8" s="2">
         <v>30021</v>
       </c>
@@ -1205,10 +1253,10 @@
         <v>3002</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G8" s="2">
         <v>3</v>
@@ -1216,9 +1264,15 @@
       <c r="H8" s="2">
         <v>1</v>
       </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1</v>
+      </c>
       <c r="L8" s="1"/>
     </row>
-    <row r="9" s="2" customFormat="1" ht="16" customHeight="1" spans="3:12">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C9" s="2">
         <v>1</v>
       </c>
@@ -1226,10 +1280,10 @@
         <v>1005</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
@@ -1237,9 +1291,15 @@
       <c r="H9" s="2">
         <v>20</v>
       </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1</v>
+      </c>
       <c r="L9" s="1"/>
     </row>
-    <row r="10" s="2" customFormat="1" ht="16" customHeight="1" spans="3:12">
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C10" s="2">
         <v>2</v>
       </c>
@@ -1247,10 +1307,10 @@
         <v>2005</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
@@ -1258,9 +1318,15 @@
       <c r="H10" s="2">
         <v>15</v>
       </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1</v>
+      </c>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" s="2" customFormat="1" ht="16" customHeight="1" spans="3:12">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C11" s="2">
         <v>3</v>
       </c>
@@ -1268,10 +1334,10 @@
         <v>3005</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
@@ -1279,9 +1345,21 @@
       <c r="H11" s="2">
         <v>10</v>
       </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1</v>
+      </c>
       <c r="L11" s="1"/>
     </row>
-    <row r="12" spans="3:8">
+    <row r="12" customHeight="1" spans="1:10">
+      <c r="A12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="C12" s="2">
         <v>4</v>
       </c>
@@ -1289,10 +1367,10 @@
         <v>1008</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1300,8 +1378,20 @@
       <c r="H12" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="3:8">
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:10">
+      <c r="A13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="C13" s="2">
         <v>5</v>
       </c>
@@ -1309,10 +1399,10 @@
         <v>2008</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -1320,8 +1410,20 @@
       <c r="H13" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="14" spans="3:8">
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:10">
+      <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="C14" s="2">
         <v>6</v>
       </c>
@@ -1329,16 +1431,196 @@
         <v>3008</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
       </c>
       <c r="H14" s="1">
         <v>50</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:10">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="2">
+        <v>7</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1009</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>100</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:10">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="2">
+        <v>8</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2009</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>100</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1</v>
+      </c>
+      <c r="J16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:10">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="2">
+        <v>9</v>
+      </c>
+      <c r="D17" s="1">
+        <v>3009</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>50</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1</v>
+      </c>
+      <c r="J17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:10">
+      <c r="C18" s="2">
+        <v>10</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1009</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>10</v>
+      </c>
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
+      <c r="J18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:10">
+      <c r="C19" s="2">
+        <v>11</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2009</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="2">
+        <v>1</v>
+      </c>
+      <c r="J19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:10">
+      <c r="C20" s="2">
+        <v>12</v>
+      </c>
+      <c r="D20" s="1">
+        <v>3009</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>20</v>
+      </c>
+      <c r="I20" s="2">
+        <v>1</v>
+      </c>
+      <c r="J20" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/SkillDivineAttrConfig.xlsx
+++ b/Excel/SkillDivineAttrConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
   <si>
     <t>_Id</t>
   </si>
@@ -1093,7 +1093,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:L20"/>
+  <dimension ref="A3:L17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1193,7 +1193,7 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C6" s="2">
-        <v>10021</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2">
         <v>1002</v>
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C7" s="2">
-        <v>20021</v>
+        <v>2</v>
       </c>
       <c r="D7" s="2">
         <v>2002</v>
@@ -1247,7 +1247,7 @@
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C8" s="2">
-        <v>30021</v>
+        <v>3</v>
       </c>
       <c r="D8" s="2">
         <v>3002</v>
@@ -1274,7 +1274,7 @@
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C9" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D9" s="2">
         <v>1005</v>
@@ -1301,7 +1301,7 @@
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C10" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" s="2">
         <v>2005</v>
@@ -1328,7 +1328,7 @@
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C11" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D11" s="2">
         <v>3005</v>
@@ -1361,7 +1361,7 @@
         <v>23</v>
       </c>
       <c r="C12" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D12" s="1">
         <v>1008</v>
@@ -1393,7 +1393,7 @@
         <v>23</v>
       </c>
       <c r="C13" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D13" s="1">
         <v>2008</v>
@@ -1425,7 +1425,7 @@
         <v>23</v>
       </c>
       <c r="C14" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D14" s="1">
         <v>3008</v>
@@ -1449,30 +1449,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:10">
-      <c r="A15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>23</v>
-      </c>
+    <row r="15" customHeight="1" spans="3:10">
       <c r="C15" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D15" s="1">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="I15" s="2">
         <v>1</v>
@@ -1481,30 +1475,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:10">
-      <c r="A16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>23</v>
-      </c>
+    <row r="16" customHeight="1" spans="3:10">
       <c r="C16" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D16" s="1">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I16" s="2">
         <v>1</v>
@@ -1513,113 +1501,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:10">
-      <c r="A17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>23</v>
-      </c>
+    <row r="17" customHeight="1" spans="3:10">
       <c r="C17" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D17" s="1">
-        <v>3009</v>
+        <v>3010</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I17" s="2">
         <v>1</v>
       </c>
       <c r="J17" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:10">
-      <c r="C18" s="2">
-        <v>10</v>
-      </c>
-      <c r="D18" s="1">
-        <v>1009</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1">
-        <v>10</v>
-      </c>
-      <c r="I18" s="2">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:10">
-      <c r="C19" s="2">
-        <v>11</v>
-      </c>
-      <c r="D19" s="1">
-        <v>2009</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20</v>
-      </c>
-      <c r="I19" s="2">
-        <v>1</v>
-      </c>
-      <c r="J19" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:10">
-      <c r="C20" s="2">
-        <v>12</v>
-      </c>
-      <c r="D20" s="1">
-        <v>3009</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
-      </c>
-      <c r="H20" s="1">
-        <v>20</v>
-      </c>
-      <c r="I20" s="2">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2">
         <v>1</v>
       </c>
     </row>

--- a/Excel/SkillDivineAttrConfig.xlsx
+++ b/Excel/SkillDivineAttrConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1379,7 +1379,7 @@
         <v>100</v>
       </c>
       <c r="I12" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J12" s="2">
         <v>1</v>
@@ -1411,7 +1411,7 @@
         <v>100</v>
       </c>
       <c r="I13" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J13" s="2">
         <v>1</v>
@@ -1443,7 +1443,7 @@
         <v>50</v>
       </c>
       <c r="I14" s="2">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="J14" s="2">
         <v>1</v>
@@ -1466,13 +1466,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I15" s="2">
         <v>1</v>
       </c>
       <c r="J15" s="2">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:10">
@@ -1498,7 +1498,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="2">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:10">
@@ -1524,7 +1524,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="2">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/SkillDivineAttrConfig.xlsx
+++ b/Excel/SkillDivineAttrConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="37">
   <si>
     <t>_Id</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>PercentRate</t>
+  </si>
+  <si>
+    <t>LevelRequire</t>
   </si>
   <si>
     <t>Id</t>
@@ -1132,12 +1135,14 @@
       <c r="J3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="3"/>
+      <c r="K3" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="L3" s="3"/>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C4" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>1</v>
@@ -1160,35 +1165,39 @@
       <c r="J4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="3"/>
+      <c r="K4" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="L4" s="3"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C5" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="I5" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="L5" s="3"/>
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:12">
@@ -1199,10 +1208,10 @@
         <v>1002</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" s="2">
         <v>2</v>
@@ -1214,6 +1223,9 @@
         <v>1</v>
       </c>
       <c r="J6" s="2">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2">
         <v>1</v>
       </c>
       <c r="L6" s="1"/>
@@ -1226,10 +1238,10 @@
         <v>2002</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -1241,6 +1253,9 @@
         <v>1</v>
       </c>
       <c r="J7" s="2">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2">
         <v>1</v>
       </c>
       <c r="L7" s="1"/>
@@ -1253,10 +1268,10 @@
         <v>3002</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" s="2">
         <v>3</v>
@@ -1268,6 +1283,9 @@
         <v>1</v>
       </c>
       <c r="J8" s="2">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2">
         <v>1</v>
       </c>
       <c r="L8" s="1"/>
@@ -1280,10 +1298,10 @@
         <v>1005</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
@@ -1295,6 +1313,9 @@
         <v>1</v>
       </c>
       <c r="J9" s="2">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2">
         <v>1</v>
       </c>
       <c r="L9" s="1"/>
@@ -1307,10 +1328,10 @@
         <v>2005</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
@@ -1322,6 +1343,9 @@
         <v>1</v>
       </c>
       <c r="J10" s="2">
+        <v>1</v>
+      </c>
+      <c r="K10" s="2">
         <v>1</v>
       </c>
       <c r="L10" s="1"/>
@@ -1334,10 +1358,10 @@
         <v>3005</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
@@ -1349,16 +1373,19 @@
         <v>1</v>
       </c>
       <c r="J11" s="2">
+        <v>1</v>
+      </c>
+      <c r="K11" s="2">
         <v>1</v>
       </c>
       <c r="L11" s="1"/>
     </row>
     <row r="12" customHeight="1" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" s="2">
         <v>7</v>
@@ -1367,10 +1394,10 @@
         <v>1008</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1387,10 +1414,10 @@
     </row>
     <row r="13" customHeight="1" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" s="2">
         <v>8</v>
@@ -1399,10 +1426,10 @@
         <v>2008</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -1419,10 +1446,10 @@
     </row>
     <row r="14" customHeight="1" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" s="2">
         <v>9</v>
@@ -1431,10 +1458,10 @@
         <v>3008</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -1449,7 +1476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:10">
+    <row r="15" customHeight="1" spans="3:11">
       <c r="C15" s="2">
         <v>10</v>
       </c>
@@ -1457,10 +1484,10 @@
         <v>1010</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -1474,8 +1501,11 @@
       <c r="J15" s="2">
         <v>25</v>
       </c>
+      <c r="K15" s="1">
+        <v>150</v>
+      </c>
     </row>
-    <row r="16" customHeight="1" spans="3:10">
+    <row r="16" customHeight="1" spans="3:11">
       <c r="C16" s="2">
         <v>11</v>
       </c>
@@ -1483,10 +1513,10 @@
         <v>2010</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -1500,8 +1530,11 @@
       <c r="J16" s="2">
         <v>25</v>
       </c>
+      <c r="K16" s="1">
+        <v>150</v>
+      </c>
     </row>
-    <row r="17" customHeight="1" spans="3:10">
+    <row r="17" customHeight="1" spans="3:11">
       <c r="C17" s="2">
         <v>12</v>
       </c>
@@ -1509,10 +1542,10 @@
         <v>3010</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -1525,6 +1558,9 @@
       </c>
       <c r="J17" s="2">
         <v>25</v>
+      </c>
+      <c r="K17" s="1">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/SkillDivineAttrConfig.xlsx
+++ b/Excel/SkillDivineAttrConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1493,16 +1493,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I15" s="2">
         <v>1</v>
       </c>
       <c r="J15" s="2">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K15" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:11">
@@ -1528,10 +1528,10 @@
         <v>1</v>
       </c>
       <c r="J16" s="2">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K16" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:11">
@@ -1557,10 +1557,10 @@
         <v>1</v>
       </c>
       <c r="J17" s="2">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K17" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/SkillDivineAttrConfig.xlsx
+++ b/Excel/SkillDivineAttrConfig.xlsx
@@ -1502,7 +1502,7 @@
         <v>50</v>
       </c>
       <c r="K15" s="1">
-        <v>120</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:11">
@@ -1531,7 +1531,7 @@
         <v>50</v>
       </c>
       <c r="K16" s="1">
-        <v>120</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:11">
@@ -1560,7 +1560,7 @@
         <v>50</v>
       </c>
       <c r="K17" s="1">
-        <v>120</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/SkillDivineAttrConfig.xlsx
+++ b/Excel/SkillDivineAttrConfig.xlsx
@@ -1499,7 +1499,7 @@
         <v>1</v>
       </c>
       <c r="J15" s="2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K15" s="1">
         <v>135</v>
@@ -1528,7 +1528,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="2">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="K16" s="1">
         <v>135</v>
@@ -1557,7 +1557,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="2">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="K17" s="1">
         <v>135</v>

--- a/Excel/SkillDivineAttrConfig.xlsx
+++ b/Excel/SkillDivineAttrConfig.xlsx
@@ -131,13 +131,13 @@
     <t>神技·分身术</t>
   </si>
   <si>
-    <t>分身享受{0}%的天赋和无视防御效果，神话之路会削弱</t>
+    <t>分身享受{0}%的天赋、无视防御、韧性效果，神话之路会削弱</t>
   </si>
   <si>
     <t>神技·无极道体</t>
   </si>
   <si>
-    <t>宠物享受{0}%的天赋和无视防御效果，神话之路会削弱</t>
+    <t>宠物享受{0}%的天赋、无视防御、韧性效果，神话之路会削弱</t>
   </si>
 </sst>
 </file>

--- a/Excel/SkillDivineAttrConfig.xlsx
+++ b/Excel/SkillDivineAttrConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
     <t>神技·无极道体</t>
   </si>
   <si>
-    <t>宠物享受{0}%的天赋、无视防御、韧性效果，神话之路会削弱</t>
+    <t>宠物享受{0}%的天赋、无视防御、韧性效果，护体神戒、神话之路会削弱</t>
   </si>
 </sst>
 </file>

--- a/Excel/SkillDivineAttrConfig.xlsx
+++ b/Excel/SkillDivineAttrConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="44">
   <si>
     <t>_Id</t>
   </si>
@@ -38,6 +38,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>Type</t>
+  </si>
+  <si>
     <t>Desc</t>
   </si>
   <si>
@@ -138,6 +141,24 @@
   </si>
   <si>
     <t>宠物享受{0}%的天赋、无视防御、韧性效果，护体神戒、神话之路会削弱</t>
+  </si>
+  <si>
+    <t>神技·武力精通</t>
+  </si>
+  <si>
+    <t>武力精通额外提高{0}%的独立增幅</t>
+  </si>
+  <si>
+    <t>神技·法力精通</t>
+  </si>
+  <si>
+    <t>法力精通额外提高{0}%的独立增幅</t>
+  </si>
+  <si>
+    <t>神技·道力精通</t>
+  </si>
+  <si>
+    <t>道力精通额外提高{0}%的独立增幅</t>
   </si>
 </sst>
 </file>
@@ -1096,21 +1117,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:L17"/>
+  <dimension ref="A3:M21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="13.375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="53" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.25" style="1" customWidth="1"/>
-    <col min="8" max="9" width="10.125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="17.25" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="5" max="6" width="13.375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="53" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.25" style="1" customWidth="1"/>
+    <col min="9" max="10" width="10.125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14.375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.25" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1138,11 +1159,14 @@
       <c r="K3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="3"/>
+      <c r="L3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="3"/>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C4" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>1</v>
@@ -1168,39 +1192,45 @@
       <c r="K4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="3"/>
+      <c r="L4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L5" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M5" s="3"/>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:12">
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="C6" s="2">
         <v>1</v>
       </c>
@@ -1208,29 +1238,32 @@
         <v>1002</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="2">
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="2">
         <v>2</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <v>30</v>
       </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
       <c r="J6" s="2">
         <v>1</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
       </c>
-      <c r="L6" s="1"/>
+      <c r="L6" s="2">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1"/>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:12">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="C7" s="2">
         <v>2</v>
       </c>
@@ -1238,13 +1271,13 @@
         <v>2002</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="2">
-        <v>1</v>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -1258,9 +1291,12 @@
       <c r="K7" s="2">
         <v>1</v>
       </c>
-      <c r="L7" s="1"/>
+      <c r="L7" s="2">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1"/>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:12">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="C8" s="2">
         <v>3</v>
       </c>
@@ -1268,17 +1304,17 @@
         <v>3002</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="2">
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="2">
         <v>3</v>
       </c>
-      <c r="H8" s="2">
-        <v>1</v>
-      </c>
       <c r="I8" s="2">
         <v>1</v>
       </c>
@@ -1288,9 +1324,12 @@
       <c r="K8" s="2">
         <v>1</v>
       </c>
-      <c r="L8" s="1"/>
+      <c r="L8" s="2">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1"/>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:12">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="C9" s="2">
         <v>4</v>
       </c>
@@ -1298,29 +1337,32 @@
         <v>1005</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="2">
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="2">
         <v>0</v>
       </c>
-      <c r="H9" s="2">
+      <c r="I9" s="2">
         <v>20</v>
       </c>
-      <c r="I9" s="2">
-        <v>1</v>
-      </c>
       <c r="J9" s="2">
         <v>1</v>
       </c>
       <c r="K9" s="2">
         <v>1</v>
       </c>
-      <c r="L9" s="1"/>
+      <c r="L9" s="2">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1"/>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:12">
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="C10" s="2">
         <v>5</v>
       </c>
@@ -1328,29 +1370,32 @@
         <v>2005</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="2">
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="2">
         <v>0</v>
       </c>
-      <c r="H10" s="2">
+      <c r="I10" s="2">
         <v>15</v>
       </c>
-      <c r="I10" s="2">
-        <v>1</v>
-      </c>
       <c r="J10" s="2">
         <v>1</v>
       </c>
       <c r="K10" s="2">
         <v>1</v>
       </c>
-      <c r="L10" s="1"/>
+      <c r="L10" s="2">
+        <v>1</v>
+      </c>
+      <c r="M10" s="1"/>
     </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:12">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="C11" s="2">
         <v>6</v>
       </c>
@@ -1358,34 +1403,37 @@
         <v>3005</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="2">
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="2">
         <v>0</v>
       </c>
-      <c r="H11" s="2">
+      <c r="I11" s="2">
         <v>10</v>
       </c>
-      <c r="I11" s="2">
-        <v>1</v>
-      </c>
       <c r="J11" s="2">
         <v>1</v>
       </c>
       <c r="K11" s="2">
         <v>1</v>
       </c>
-      <c r="L11" s="1"/>
+      <c r="L11" s="2">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1"/>
     </row>
-    <row r="12" customHeight="1" spans="1:10">
+    <row r="12" customHeight="1" spans="1:13">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" s="2">
         <v>7</v>
@@ -1394,30 +1442,33 @@
         <v>1008</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>100</v>
+      </c>
+      <c r="J12" s="2">
+        <v>100</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:13">
+      <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1">
-        <v>100</v>
-      </c>
-      <c r="I12" s="2">
-        <v>100</v>
-      </c>
-      <c r="J12" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:10">
-      <c r="A13" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2">
         <v>8</v>
@@ -1426,30 +1477,33 @@
         <v>2008</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="1">
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="1">
         <v>0</v>
       </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
         <v>100</v>
       </c>
-      <c r="I13" s="2">
+      <c r="J13" s="2">
         <v>100</v>
       </c>
-      <c r="J13" s="2">
+      <c r="K13" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:10">
+    <row r="14" customHeight="1" spans="1:13">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" s="2">
         <v>9</v>
@@ -1458,25 +1512,28 @@
         <v>3008</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="1">
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="1">
         <v>0</v>
       </c>
-      <c r="H14" s="1">
+      <c r="I14" s="1">
         <v>50</v>
       </c>
-      <c r="I14" s="2">
+      <c r="J14" s="2">
         <v>50</v>
       </c>
-      <c r="J14" s="2">
+      <c r="K14" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:11">
+    <row r="15" customHeight="1" spans="1:13">
       <c r="C15" s="2">
         <v>10</v>
       </c>
@@ -1484,28 +1541,31 @@
         <v>1010</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="1">
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="1">
         <v>0</v>
       </c>
-      <c r="H15" s="1">
+      <c r="I15" s="1">
         <v>12</v>
       </c>
-      <c r="I15" s="2">
-        <v>1</v>
-      </c>
       <c r="J15" s="2">
+        <v>1</v>
+      </c>
+      <c r="K15" s="2">
         <v>100</v>
       </c>
-      <c r="K15" s="1">
+      <c r="L15" s="1">
         <v>135</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="3:11">
+    <row r="16" customHeight="1" spans="1:13">
       <c r="C16" s="2">
         <v>11</v>
       </c>
@@ -1513,28 +1573,31 @@
         <v>2010</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G16" s="1">
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="1">
         <v>0</v>
       </c>
-      <c r="H16" s="1">
+      <c r="I16" s="1">
         <v>20</v>
       </c>
-      <c r="I16" s="2">
-        <v>1</v>
-      </c>
       <c r="J16" s="2">
+        <v>1</v>
+      </c>
+      <c r="K16" s="2">
         <v>7</v>
       </c>
-      <c r="K16" s="1">
+      <c r="L16" s="1">
         <v>135</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="3:11">
+    <row r="17" customHeight="1" spans="3:12">
       <c r="C17" s="2">
         <v>12</v>
       </c>
@@ -1542,30 +1605,129 @@
         <v>3010</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G17" s="1">
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="1">
         <v>0</v>
       </c>
-      <c r="H17" s="1">
+      <c r="I17" s="1">
         <v>20</v>
       </c>
-      <c r="I17" s="2">
-        <v>1</v>
-      </c>
       <c r="J17" s="2">
+        <v>1</v>
+      </c>
+      <c r="K17" s="2">
         <v>5</v>
       </c>
-      <c r="K17" s="1">
+      <c r="L17" s="1">
         <v>135</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:12">
+      <c r="C19" s="2">
+        <v>13</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1006</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" s="2">
+        <v>2</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>25</v>
+      </c>
+      <c r="J19" s="2">
+        <v>1</v>
+      </c>
+      <c r="K19" s="2">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:12">
+      <c r="C20" s="2">
+        <v>14</v>
+      </c>
+      <c r="D20" s="2">
+        <v>2006</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" s="2">
+        <v>2</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2">
+        <v>25</v>
+      </c>
+      <c r="J20" s="2">
+        <v>1</v>
+      </c>
+      <c r="K20" s="2">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:12">
+      <c r="C21" s="2">
+        <v>15</v>
+      </c>
+      <c r="D21" s="2">
+        <v>3006</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="2">
+        <v>2</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>25</v>
+      </c>
+      <c r="J21" s="2">
+        <v>1</v>
+      </c>
+      <c r="K21" s="2">
+        <v>1</v>
+      </c>
+      <c r="L21" s="2">
+        <v>5000</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:G3 E4:G4 E5:F5 C3:C5 D4:D5 L3:L5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C5:G5 M3:M5 C3:H4" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillDivineAttrConfig.xlsx
+++ b/Excel/SkillDivineAttrConfig.xlsx
@@ -1649,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J19" s="2">
         <v>1</v>
@@ -1681,7 +1681,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J20" s="2">
         <v>1</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J21" s="2">
         <v>1</v>
